--- a/data/trans_orig/P1411-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P1411-Clase-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de infarto de miocardio en 2012</t>
+          <t>Población con diagnóstico de infarto de miocardio en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5410</t>
+          <t>6097</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20689</t>
+          <t>21259</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6546</t>
+          <t>5953</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6150</t>
+          <t>6345</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20840</t>
+          <t>22588</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>416522</t>
+          <t>415952</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>431801</t>
+          <t>431114</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>307908</t>
+          <t>308501</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>730825</t>
+          <t>729077</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>745515</t>
+          <t>745320</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,16%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3214</t>
+          <t>3179</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16042</t>
+          <t>16401</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2120</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3222</t>
+          <t>4037</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17585</t>
+          <t>17390</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,3%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>402755</t>
+          <t>402396</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>415583</t>
+          <t>415618</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>335891</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>338011</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>739223</t>
+          <t>739418</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>753586</t>
+          <t>752771</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,47%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5523</t>
+          <t>5331</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21997</t>
+          <t>21868</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2038</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6141</t>
+          <t>6195</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22720</t>
+          <t>22304</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>607418</t>
+          <t>607547</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>623892</t>
+          <t>624084</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>258091</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>260129</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>866824</t>
+          <t>867240</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>883403</t>
+          <t>883349</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,3%</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23026</t>
+          <t>22395</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>44773</t>
+          <t>44687</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1800,7 +1800,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12594</t>
+          <t>12031</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>26518</t>
+          <t>26264</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>52503</t>
+          <t>51698</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1114236</t>
+          <t>1114322</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1135983</t>
+          <t>1136614</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,7 +1908,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>752128</t>
+          <t>752691</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1871228</t>
+          <t>1872033</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1897213</t>
+          <t>1897467</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,63%</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2222</t>
+          <t>2237</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12533</t>
+          <t>12574</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>7530</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>24510</t>
+          <t>23653</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2153,12 +2153,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>12078</t>
+          <t>12309</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>30051</t>
+          <t>30674</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,41%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>498063</t>
+          <t>498022</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>508374</t>
+          <t>508359</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>735736</t>
+          <t>736593</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>752194</t>
+          <t>752716</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1240792</t>
+          <t>1240169</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1258765</t>
+          <t>1258534</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,03%</t>
         </is>
       </c>
     </row>
@@ -2451,7 +2451,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4109</t>
+          <t>5138</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2481,12 +2481,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10617</t>
+          <t>10366</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>27436</t>
+          <t>27296</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2516,12 +2516,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>10470</t>
+          <t>10396</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>26969</t>
+          <t>27218</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2536,7 +2536,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,98%</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>262773</t>
+          <t>261744</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2594,12 +2594,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1080733</t>
+          <t>1080873</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1097552</t>
+          <t>1097803</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2609,12 +2609,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1348082</t>
+          <t>1347833</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1364581</t>
+          <t>1364655</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2789,12 +2789,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>54387</t>
+          <t>54700</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>88573</t>
+          <t>90389</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2804,12 +2804,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>28136</t>
+          <t>27055</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>52467</t>
+          <t>51530</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2839,12 +2839,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>88470</t>
+          <t>89329</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>131629</t>
+          <t>130742</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2874,12 +2874,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -2902,12 +2902,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3333337</t>
+          <t>3331521</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3367523</t>
+          <t>3367210</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2917,12 +2917,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3493265</t>
+          <t>3494202</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3517596</t>
+          <t>3518677</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2952,12 +2952,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6836013</t>
+          <t>6836900</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6879172</t>
+          <t>6878313</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2987,12 +2987,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,72%</t>
         </is>
       </c>
     </row>
@@ -3171,7 +3171,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de infarto de miocardio en 2016</t>
+          <t>Población con diagnóstico de infarto de miocardio en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1780</t>
+          <t>1745</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10577</t>
+          <t>10857</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12179</t>
+          <t>11879</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3421,7 +3421,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5448</t>
+          <t>5012</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20050</t>
+          <t>17801</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>418515</t>
+          <t>418235</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>427312</t>
+          <t>427347</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3494,7 +3494,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>334876</t>
+          <t>335176</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>345012</t>
+          <t>344996</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>756097</t>
+          <t>758346</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>770699</t>
+          <t>771135</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,35%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1825</t>
+          <t>1722</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10816</t>
+          <t>10538</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1808</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10492</t>
+          <t>10473</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>366411</t>
+          <t>366689</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>375402</t>
+          <t>375505</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>370249</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>372273</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>739008</t>
+          <t>739027</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>747692</t>
+          <t>748290</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3912,7 +3912,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,84%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8218</t>
+          <t>9013</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23986</t>
+          <t>25960</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2069</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8811</t>
+          <t>7866</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>25442</t>
+          <t>24108</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,5%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>497928</t>
+          <t>495954</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>513696</t>
+          <t>512901</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>164054</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>166123</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>662594</t>
+          <t>663928</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>679225</t>
+          <t>680170</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,86%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15263</t>
+          <t>15778</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>34055</t>
+          <t>34739</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3659</t>
+          <t>4319</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17013</t>
+          <t>16969</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>22458</t>
+          <t>22854</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>45979</t>
+          <t>46770</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,37%</t>
         </is>
       </c>
     </row>
@@ -4508,12 +4508,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1115583</t>
+          <t>1114899</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1134375</t>
+          <t>1133860</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4523,12 +4523,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4543,12 +4543,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>808863</t>
+          <t>808907</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>822217</t>
+          <t>821557</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4558,12 +4558,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4578,12 +4578,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1929535</t>
+          <t>1928744</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1953056</t>
+          <t>1952660</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4593,12 +4593,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,84%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11579</t>
+          <t>11789</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28092</t>
+          <t>28155</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6188</t>
+          <t>5849</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21691</t>
+          <t>21463</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>20465</t>
+          <t>20036</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>45691</t>
+          <t>42575</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,13%</t>
         </is>
       </c>
     </row>
@@ -4851,12 +4851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>592614</t>
+          <t>592551</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>609127</t>
+          <t>608917</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4866,12 +4866,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4886,12 +4886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>716553</t>
+          <t>716781</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>732056</t>
+          <t>732395</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4901,12 +4901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4921,12 +4921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1313259</t>
+          <t>1316375</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1338485</t>
+          <t>1338914</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4936,12 +4936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,53%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10051</t>
+          <t>10338</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>28533</t>
+          <t>27404</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>10641</t>
+          <t>11302</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>28245</t>
+          <t>28303</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -5194,12 +5194,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>285126</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>287145</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5229,12 +5229,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1053492</t>
+          <t>1054621</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1071974</t>
+          <t>1071687</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5244,12 +5244,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5264,12 +5264,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1340925</t>
+          <t>1340867</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1358529</t>
+          <t>1357868</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5279,12 +5279,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,17%</t>
         </is>
       </c>
     </row>
@@ -5424,12 +5424,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>52528</t>
+          <t>53285</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>86286</t>
+          <t>84021</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5439,12 +5439,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5459,12 +5459,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>32185</t>
+          <t>32174</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>60901</t>
+          <t>60758</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5494,12 +5494,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>91692</t>
+          <t>89788</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>136148</t>
+          <t>133084</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5509,12 +5509,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -5537,12 +5537,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3299436</t>
+          <t>3301701</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3333194</t>
+          <t>3332437</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5552,12 +5552,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5572,12 +5572,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3470695</t>
+          <t>3470838</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3499411</t>
+          <t>3499422</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6781170</t>
+          <t>6784234</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6825626</t>
+          <t>6827530</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,7%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1411-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P1411-Clase-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6097</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21259</t>
+          <t>20899</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5953</t>
+          <t>5326</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6345</t>
+          <t>6265</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22588</t>
+          <t>22083</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,94%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>415952</t>
+          <t>416312</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>431114</t>
+          <t>431947</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>308501</t>
+          <t>309128</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>729077</t>
+          <t>729582</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>745320</t>
+          <t>745400</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,17%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3179</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16401</t>
+          <t>17978</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4037</t>
+          <t>3215</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17390</t>
+          <t>18384</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>402396</t>
+          <t>400819</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>415618</t>
+          <t>415566</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>739418</t>
+          <t>738424</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>752771</t>
+          <t>753593</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,58%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5331</t>
+          <t>6147</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21868</t>
+          <t>20882</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6195</t>
+          <t>6122</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22304</t>
+          <t>21732</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,44%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>607547</t>
+          <t>608533</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>624084</t>
+          <t>623268</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>867240</t>
+          <t>867812</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>883349</t>
+          <t>883422</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,31%</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22395</t>
+          <t>22422</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>44687</t>
+          <t>45509</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2101</t>
+          <t>2999</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12031</t>
+          <t>13348</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>26264</t>
+          <t>27247</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>51698</t>
+          <t>52076</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,71%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1114322</t>
+          <t>1113500</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1136614</t>
+          <t>1136587</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>752691</t>
+          <t>751374</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>762621</t>
+          <t>761723</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1872033</t>
+          <t>1871655</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1897467</t>
+          <t>1896484</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,58%</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2237</t>
+          <t>2196</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12574</t>
+          <t>12333</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7530</t>
+          <t>7347</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>23653</t>
+          <t>23839</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2153,12 +2153,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>12309</t>
+          <t>12441</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>30674</t>
+          <t>31378</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,47%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>498022</t>
+          <t>498263</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>508359</t>
+          <t>508400</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,12 +2231,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>736593</t>
+          <t>736407</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>752716</t>
+          <t>752899</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1240169</t>
+          <t>1239465</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1258534</t>
+          <t>1258402</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,02%</t>
         </is>
       </c>
     </row>
@@ -2426,7 +2426,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5138</t>
+          <t>5006</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2481,12 +2481,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10366</t>
+          <t>9664</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>27296</t>
+          <t>25918</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2516,12 +2516,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>10396</t>
+          <t>11185</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>27218</t>
+          <t>27518</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>261744</t>
+          <t>261876</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2594,12 +2594,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1080873</t>
+          <t>1082251</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1097803</t>
+          <t>1098505</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2609,12 +2609,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1347833</t>
+          <t>1347533</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1364655</t>
+          <t>1363866</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2644,12 +2644,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,19%</t>
         </is>
       </c>
     </row>
@@ -2789,12 +2789,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>54700</t>
+          <t>53075</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>90389</t>
+          <t>89657</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2804,12 +2804,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>27055</t>
+          <t>27719</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>51530</t>
+          <t>52537</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2839,12 +2839,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>89329</t>
+          <t>90615</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>130742</t>
+          <t>132005</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2874,12 +2874,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -2902,12 +2902,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3331521</t>
+          <t>3332253</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3367210</t>
+          <t>3368835</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2917,12 +2917,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3494202</t>
+          <t>3493195</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3518677</t>
+          <t>3518013</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2952,12 +2952,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6836900</t>
+          <t>6835637</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6878313</t>
+          <t>6877027</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2987,12 +2987,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,7%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1745</t>
+          <t>1837</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10857</t>
+          <t>11270</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>2092</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11879</t>
+          <t>12027</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5012</t>
+          <t>5372</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17801</t>
+          <t>17619</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,27%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>418235</t>
+          <t>417822</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>427347</t>
+          <t>427255</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>335176</t>
+          <t>335028</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>344996</t>
+          <t>344963</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>758346</t>
+          <t>758528</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>771135</t>
+          <t>770775</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,31%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1722</t>
+          <t>1808</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10538</t>
+          <t>10482</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1210</t>
+          <t>1772</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10473</t>
+          <t>10988</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>366689</t>
+          <t>366745</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>375505</t>
+          <t>375419</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>739027</t>
+          <t>738512</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>748290</t>
+          <t>747728</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,76%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9013</t>
+          <t>8140</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25960</t>
+          <t>24172</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7866</t>
+          <t>8431</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>24108</t>
+          <t>24747</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,6%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>495954</t>
+          <t>497742</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>512901</t>
+          <t>513774</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>663928</t>
+          <t>663289</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>680170</t>
+          <t>679605</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,77%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15778</t>
+          <t>15188</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>34739</t>
+          <t>34664</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4410,7 +4410,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4319</t>
+          <t>4182</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16969</t>
+          <t>16906</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>22854</t>
+          <t>22532</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>46770</t>
+          <t>45627</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,31%</t>
         </is>
       </c>
     </row>
@@ -4508,12 +4508,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1114899</t>
+          <t>1114974</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1133860</t>
+          <t>1134450</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4528,7 +4528,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4543,12 +4543,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>808907</t>
+          <t>808970</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>821557</t>
+          <t>821694</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4563,7 +4563,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4578,12 +4578,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1928744</t>
+          <t>1929887</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1952660</t>
+          <t>1952982</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4593,12 +4593,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,86%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11789</t>
+          <t>11872</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28155</t>
+          <t>27994</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5849</t>
+          <t>6259</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21463</t>
+          <t>21016</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>20036</t>
+          <t>20744</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>42575</t>
+          <t>42088</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,1%</t>
         </is>
       </c>
     </row>
@@ -4851,12 +4851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>592551</t>
+          <t>592712</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>608917</t>
+          <t>608834</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4866,12 +4866,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4886,12 +4886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>716781</t>
+          <t>717228</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>732395</t>
+          <t>731985</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4901,12 +4901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4921,12 +4921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1316375</t>
+          <t>1316862</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1338914</t>
+          <t>1338206</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4936,12 +4936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,47%</t>
         </is>
       </c>
     </row>
@@ -5061,7 +5061,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10338</t>
+          <t>11081</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>27404</t>
+          <t>29684</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>11302</t>
+          <t>10275</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>28303</t>
+          <t>28189</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -5229,12 +5229,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1054621</t>
+          <t>1052341</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1071687</t>
+          <t>1070944</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5244,12 +5244,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5264,12 +5264,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1340867</t>
+          <t>1340981</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1357868</t>
+          <t>1358895</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5279,12 +5279,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,25%</t>
         </is>
       </c>
     </row>
@@ -5424,12 +5424,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>53285</t>
+          <t>54037</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>84021</t>
+          <t>85181</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5439,12 +5439,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5459,12 +5459,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>32174</t>
+          <t>30791</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>60758</t>
+          <t>60152</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5474,12 +5474,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5494,12 +5494,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>89788</t>
+          <t>91479</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>133084</t>
+          <t>134764</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5509,12 +5509,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,95%</t>
         </is>
       </c>
     </row>
@@ -5537,12 +5537,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3301701</t>
+          <t>3300541</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3332437</t>
+          <t>3331685</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5552,12 +5552,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5572,12 +5572,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3470838</t>
+          <t>3471444</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3499422</t>
+          <t>3500805</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5587,12 +5587,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6784234</t>
+          <t>6782554</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6827530</t>
+          <t>6825839</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,68%</t>
         </is>
       </c>
     </row>
